--- a/analysis/combined_2025_26.xlsx
+++ b/analysis/combined_2025_26.xlsx
@@ -4388,7 +4388,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Reece James</t>
+          <t>Nordi Mukiele</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4413,12 +4413,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Cody Gakpo</t>
+          <t>Reece James</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Dominik Szoboszlai</t>
+          <t>Bruno Borges Fernandes</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -4463,47 +4463,47 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
+          <t>Dominik Szoboszlai</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>10</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
           <t>Ismaïla Sarr</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B192" s="3" t="inlineStr">
-        <is>
-          <t>Erling Haaland</t>
-        </is>
-      </c>
-      <c r="C192" s="3" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D192" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
     </row>
@@ -4513,47 +4513,47 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Norberto Bercique Gomes Betuncal</t>
+          <t>Tijjani Reijnders</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>Erling Haaland</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
           <t>FWD</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>10</v>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Richarlison de Andrade</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Bruno Borges Fernandes</t>
+          <t>Cody Gakpo</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Nordi Mukiele</t>
+          <t>Norberto Bercique Gomes Betuncal</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Tijjani Reijnders</t>
+          <t>Richarlison de Andrade</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4668,7 +4668,7 @@
       <c r="D199" s="5" t="inlineStr"/>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>68  [Bench Boost week: bench 13 not in path; chip read]</t>
+          <t>70  [Bench Boost week: bench 11 not in path; chip read]</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Lewis Miley</t>
+          <t>Matheus Santos Carneiro da Cunha</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Matheus Santos Carneiro da Cunha</t>
+          <t>Rayan Cherki</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       <c r="D381" s="5" t="inlineStr"/>
       <c r="E381" s="5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       <c r="A382" t="inlineStr"/>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Lewis Miley in for Tijjani Reijnders</t>
+          <t>Rayan Cherki in for Tijjani Reijnders</t>
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Lewis Miley</t>
+          <t>Enzo Fernández</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="B393" s="3" t="inlineStr">
         <is>
-          <t>Phil Foden</t>
+          <t>Rayan Cherki</t>
         </is>
       </c>
       <c r="C393" s="3" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="E393" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       <c r="D399" s="5" t="inlineStr"/>
       <c r="E399" s="5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
       <c r="A400" t="inlineStr"/>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Phil Foden in for Dominik Szoboszlai</t>
+          <t>Enzo Fernández in for Dominik Szoboszlai</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
@@ -9142,27 +9142,27 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="n">
+      <c r="A403" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>Cristian Romero</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="B403" s="4" t="inlineStr">
+        <is>
+          <t>Ibrahima Konaté</t>
+        </is>
+      </c>
+      <c r="C403" s="4" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D403" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E403" s="4" t="inlineStr">
+        <is>
+          <t>2 (4)</t>
         </is>
       </c>
     </row>
@@ -9267,25 +9267,25 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="3" t="n">
+      <c r="A408" t="n">
         <v>22</v>
       </c>
-      <c r="B408" s="3" t="inlineStr">
+      <c r="B408" t="inlineStr">
         <is>
           <t>Antoine Semenyo</t>
         </is>
       </c>
-      <c r="C408" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D408" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E408" s="3" t="inlineStr">
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Lewis Miley</t>
+          <t>Enzo Fernández</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Phil Foden</t>
+          <t>Rayan Cherki</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -9367,27 +9367,27 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="4" t="n">
+      <c r="A412" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B412" s="4" t="inlineStr">
+      <c r="B412" s="3" t="inlineStr">
         <is>
           <t>Erling Haaland</t>
         </is>
       </c>
-      <c r="C412" s="4" t="inlineStr">
+      <c r="C412" s="3" t="inlineStr">
         <is>
           <t>FWD</t>
         </is>
       </c>
-      <c r="D412" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E412" s="4" t="inlineStr">
-        <is>
-          <t>2 (4)</t>
+      <c r="D412" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E412" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
       <c r="D417" s="5" t="inlineStr"/>
       <c r="E417" s="5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       <c r="A418" t="inlineStr"/>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Cristian Romero in for Nico O'Reilly</t>
+          <t>Ibrahima Konaté in for Nico O'Reilly</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Cristian Romero</t>
+          <t>Malick Thiaw</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Malick Thiaw</t>
+          <t>Nordi Mukiele</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Nordi Mukiele</t>
+          <t>Trevoh Chalobah</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Trevoh Chalobah</t>
+          <t>Tyrick Mitchell</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -9638,57 +9638,57 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="n">
+      <c r="A425" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Tyrick Mitchell</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="B425" s="4" t="inlineStr">
+        <is>
+          <t>Antoine Semenyo</t>
+        </is>
+      </c>
+      <c r="C425" s="4" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D425" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E425" s="4" t="inlineStr">
+        <is>
+          <t>8 (16)</t>
         </is>
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="4" t="n">
+      <c r="A426" t="n">
         <v>23</v>
       </c>
-      <c r="B426" s="4" t="inlineStr">
-        <is>
-          <t>Antoine Semenyo</t>
-        </is>
-      </c>
-      <c r="C426" s="4" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D426" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E426" s="4" t="inlineStr">
-        <is>
-          <t>8 (16)</t>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Bukayo Saka</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Bukayo Saka</t>
+          <t>Declan Rice</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Declan Rice</t>
+          <t>Enzo Fernández</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Phil Foden</t>
+          <t>Rayan Cherki</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -9823,12 +9823,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Lewis Miley</t>
+          <t>Norberto Bercique Gomes Betuncal</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9848,12 +9848,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Norberto Bercique Gomes Betuncal</t>
+          <t>Ibrahima Konaté</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       <c r="D435" s="5" t="inlineStr"/>
       <c r="E435" s="5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -9949,7 +9949,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Cristian Romero</t>
+          <t>Daniel Ballard</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Malick Thiaw</t>
+          <t>Ibrahima Konaté</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -10149,12 +10149,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Erling Haaland</t>
+          <t>Rayan Cherki</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Norberto Bercique Gomes Betuncal</t>
+          <t>Erling Haaland</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -10224,12 +10224,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Lewis Miley</t>
+          <t>Norberto Bercique Gomes Betuncal</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10304,7 @@
       <c r="D453" s="5" t="inlineStr"/>
       <c r="E453" s="5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>80</t>
         </is>
       </c>
     </row>
@@ -10312,7 +10312,7 @@
       <c r="A454" t="inlineStr"/>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Enzo Fernández in for Phil Foden</t>
+          <t>Daniel Ballard in for Malick Thiaw</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
@@ -10350,7 +10350,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Cristian Romero</t>
+          <t>Daniel Ballard</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Malick Thiaw</t>
+          <t>Ibrahima Konaté</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Tyrick Mitchell</t>
+          <t>Antoine Semenyo</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -10475,7 +10475,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Antoine Semenyo</t>
+          <t>Bryan Mbeumo</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B463" s="3" t="inlineStr">
         <is>
-          <t>Bruno Borges Fernandes</t>
+          <t>Declan Rice</t>
         </is>
       </c>
       <c r="C463" s="3" t="inlineStr">
@@ -10515,7 +10515,7 @@
       </c>
       <c r="E463" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -10525,7 +10525,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Declan Rice</t>
+          <t>Enzo Fernández</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Enzo Fernández</t>
+          <t>Rayan Cherki</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10625,12 +10625,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Lewis Miley</t>
+          <t>Nordi Mukiele</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10705,7 +10705,7 @@
       <c r="D471" s="5" t="inlineStr"/>
       <c r="E471" s="5" t="inlineStr">
         <is>
-          <t>57 (53 after hits)</t>
+          <t>54 (50 after hits)</t>
         </is>
       </c>
     </row>
@@ -10713,7 +10713,7 @@
       <c r="A472" t="inlineStr"/>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Bruno Borges Fernandes in for Bukayo Saka</t>
+          <t>Bryan Mbeumo in for Bukayo Saka</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
@@ -10724,7 +10724,7 @@
       <c r="A473" t="inlineStr"/>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Gabriel dos Santos Magalhães in for Nordi Mukiele (-4 hit)</t>
+          <t>Gabriel dos Santos Magalhães in for Tyrick Mitchell (-4 hit)</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Malick Thiaw</t>
+          <t>Ibrahima Konaté</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -10837,12 +10837,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Tyrick Mitchell</t>
+          <t>Antoine Semenyo</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Antoine Semenyo</t>
+          <t>Bryan Mbeumo</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -10877,57 +10877,57 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B481" s="3" t="inlineStr">
+        <is>
+          <t>Declan Rice</t>
+        </is>
+      </c>
+      <c r="C481" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D481" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E481" s="3" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
     </row>
-    <row r="481">
-      <c r="A481" t="n">
+    <row r="482">
+      <c r="A482" t="n">
         <v>26</v>
       </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>Bruno Borges Fernandes</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E481" t="inlineStr">
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Enzo Fernández</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B482" s="3" t="inlineStr">
-        <is>
-          <t>Declan Rice</t>
-        </is>
-      </c>
-      <c r="C482" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D482" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E482" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
     </row>
@@ -10937,7 +10937,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Enzo Fernández</t>
+          <t>Rayan Cherki</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -11037,12 +11037,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Lewis Miley</t>
+          <t>Daniel Ballard</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -11062,12 +11062,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Norberto Bercique Gomes Betuncal</t>
+          <t>Nordi Mukiele</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Cristian Romero</t>
+          <t>Norberto Bercique Gomes Betuncal</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -11117,7 +11117,7 @@
       <c r="D490" s="5" t="inlineStr"/>
       <c r="E490" s="5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Gabriel dos Santos Magalhães</t>
+          <t>Daniel Ballard</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Marc Guéhi</t>
+          <t>Gabriel dos Santos Magalhães</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -11219,52 +11219,52 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="3" t="n">
+      <c r="A497" t="n">
         <v>27</v>
       </c>
-      <c r="B497" s="3" t="inlineStr">
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Ibrahima Konaté</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B498" s="3" t="inlineStr">
         <is>
           <t>Trevoh Chalobah</t>
         </is>
       </c>
-      <c r="C497" s="3" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D497" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E497" s="3" t="inlineStr">
+      <c r="C498" s="3" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D498" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E498" s="3" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="n">
-        <v>27</v>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>Tyrick Mitchell</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E498" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Bruno Borges Fernandes</t>
+          <t>Bryan Mbeumo</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Declan Rice</t>
+          <t>Cody Gakpo</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -11349,7 +11349,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Enzo Fernández</t>
+          <t>Declan Rice</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -11374,12 +11374,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Adam Armstrong</t>
+          <t>Enzo Fernández</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Malick Thiaw</t>
+          <t>Nordi Mukiele</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Norberto Bercique Gomes Betuncal</t>
+          <t>Adam Armstrong</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -11499,12 +11499,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Lewis Miley</t>
+          <t>Norberto Bercique Gomes Betuncal</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11529,7 @@
       <c r="D509" s="5" t="inlineStr"/>
       <c r="E509" s="5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       <c r="A510" t="inlineStr"/>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Marc Guéhi in for Cristian Romero</t>
+          <t>Cody Gakpo in for Rayan Cherki</t>
         </is>
       </c>
       <c r="C510" t="inlineStr"/>
@@ -11570,52 +11570,52 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="3" t="n">
+      <c r="A513" t="n">
         <v>28</v>
       </c>
-      <c r="B513" s="3" t="inlineStr">
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Daniel Ballard</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B514" s="4" t="inlineStr">
         <is>
           <t>Gabriel dos Santos Magalhães</t>
         </is>
       </c>
-      <c r="C513" s="3" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D513" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E513" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="n">
-        <v>28</v>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>Ibrahima Konaté</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E514" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="C514" s="4" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D514" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E514" s="4" t="inlineStr">
+        <is>
+          <t>9 (18)</t>
         </is>
       </c>
     </row>
@@ -11625,7 +11625,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Malick Thiaw</t>
+          <t>Ibrahima Konaté</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -11670,27 +11670,27 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" t="n">
+      <c r="A517" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>Trevoh Chalobah</t>
-        </is>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E517" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="B517" s="3" t="inlineStr">
+        <is>
+          <t>Antoine Semenyo</t>
+        </is>
+      </c>
+      <c r="C517" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D517" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E517" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11700,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Antoine Semenyo</t>
+          <t>Bryan Mbeumo</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -11715,32 +11715,32 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="4" t="n">
+      <c r="A519" t="n">
         <v>28</v>
       </c>
-      <c r="B519" s="4" t="inlineStr">
-        <is>
-          <t>Bruno Borges Fernandes</t>
-        </is>
-      </c>
-      <c r="C519" s="4" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D519" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E519" s="4" t="inlineStr">
-        <is>
-          <t>13 (26)</t>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Cody Gakpo</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -11875,12 +11875,12 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Lewis Miley</t>
+          <t>Nordi Mukiele</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -11930,7 +11930,7 @@
       <c r="D527" s="5" t="inlineStr"/>
       <c r="E527" s="5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -11938,7 +11938,7 @@
       <c r="A528" t="inlineStr"/>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Ibrahima Konaté in for Tyrick Mitchell</t>
+          <t>Marc Guéhi in for Trevoh Chalobah</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Gabriel dos Santos Magalhães</t>
+          <t>Daniel Ballard</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Ibrahima Konaté</t>
+          <t>Gabriel dos Santos Magalhães</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Malick Thiaw</t>
+          <t>Ibrahima Konaté</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Trevoh Chalobah</t>
+          <t>Pascal Struijk</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Bruno Borges Fernandes</t>
+          <t>Bryan Mbeumo</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -12251,12 +12251,12 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Adam Armstrong</t>
+          <t>Declan Rice</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12276,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Norberto Bercique Gomes Betuncal</t>
+          <t>Adam Armstrong</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -12301,12 +12301,12 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Lewis Miley</t>
+          <t>Norberto Bercique Gomes Betuncal</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12331,7 +12331,7 @@
       <c r="D545" s="5" t="inlineStr"/>
       <c r="E545" s="5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       <c r="A546" t="inlineStr"/>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Cody Gakpo in for Declan Rice</t>
+          <t>Pascal Struijk in for Nordi Mukiele</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
@@ -12372,52 +12372,52 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="4" t="n">
+      <c r="A549" t="n">
         <v>30</v>
       </c>
-      <c r="B549" s="4" t="inlineStr">
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Daniel Ballard</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B550" s="4" t="inlineStr">
         <is>
           <t>Gabriel dos Santos Magalhães</t>
         </is>
       </c>
-      <c r="C549" s="4" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D549" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E549" s="4" t="inlineStr">
+      <c r="C550" s="4" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D550" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E550" s="4" t="inlineStr">
         <is>
           <t>9 (18)</t>
-        </is>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="n">
-        <v>30</v>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>Malick Thiaw</t>
-        </is>
-      </c>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E550" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Trevoh Chalobah</t>
+          <t>Pascal Struijk</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -12467,57 +12467,57 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B553" s="3" t="inlineStr">
+        <is>
+          <t>Antoine Semenyo</t>
+        </is>
+      </c>
+      <c r="C553" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D553" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E553" s="3" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
     </row>
-    <row r="553">
-      <c r="A553" t="n">
+    <row r="554">
+      <c r="A554" t="n">
         <v>30</v>
       </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>Antoine Semenyo</t>
-        </is>
-      </c>
-      <c r="C553" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E553" t="inlineStr">
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Bryan Mbeumo</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B554" s="3" t="inlineStr">
-        <is>
-          <t>Bruno Borges Fernandes</t>
-        </is>
-      </c>
-      <c r="C554" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D554" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E554" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
     </row>
@@ -12552,7 +12552,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Enzo Fernández</t>
+          <t>Declan Rice</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -12577,12 +12577,12 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Adam Armstrong</t>
+          <t>Enzo Fernández</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -12592,7 +12592,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Đorđe Petrović</t>
+          <t>Emiliano Martínez Romero</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12652,7 +12652,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Norberto Bercique Gomes Betuncal</t>
+          <t>Adam Armstrong</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -12677,12 +12677,12 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Lewis Miley</t>
+          <t>Norberto Bercique Gomes Betuncal</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12732,7 +12732,7 @@
       <c r="D563" s="5" t="inlineStr"/>
       <c r="E563" s="5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>53</t>
         </is>
       </c>
     </row>
@@ -12740,7 +12740,7 @@
       <c r="A564" t="inlineStr"/>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Đorđe Petrović in for Robin Roefs</t>
+          <t>Emiliano Martínez Romero in for Robin Roefs</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
@@ -12753,7 +12753,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Đorđe Petrović</t>
+          <t>Emiliano Martínez Romero</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -12768,7 +12768,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -12828,7 +12828,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Virgil van Dijk</t>
+          <t>Pascal Struijk</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Trevoh Chalobah</t>
+          <t>Daniel Ballard</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Adam Armstrong</t>
+          <t>Gabriel dos Santos Magalhães</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -13103,12 +13103,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Marc Guéhi</t>
+          <t>Adam Armstrong</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -13133,7 +13133,7 @@
       <c r="D581" s="5" t="inlineStr"/>
       <c r="E581" s="5" t="inlineStr">
         <is>
-          <t>59 (47 after hits)</t>
+          <t>65 (53 after hits)</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13141,7 @@
       <c r="A582" t="inlineStr"/>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Virgil van Dijk in for Gabriel dos Santos Magalhães</t>
+          <t>Cole Palmer in for Declan Rice</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
@@ -13152,7 +13152,7 @@
       <c r="A583" t="inlineStr"/>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Bryan Mbeumo in for Antoine Semenyo (-4 hit)</t>
+          <t>Bruno Borges Fernandes in for Antoine Semenyo (-4 hit)</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
@@ -13163,7 +13163,7 @@
       <c r="A584" t="inlineStr"/>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Igor Thiago Nascimento Rodrigues in for Erling Haaland (-4 hit)</t>
+          <t>Malick Thiaw in for Marc Guéhi (-4 hit)</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
@@ -13174,7 +13174,7 @@
       <c r="A585" t="inlineStr"/>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Cole Palmer in for Lewis Miley (-4 hit)</t>
+          <t>Igor Thiago Nascimento Rodrigues in for Erling Haaland (-4 hit)</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
@@ -13182,27 +13182,27 @@
       <c r="E585" t="inlineStr"/>
     </row>
     <row r="587">
-      <c r="A587" t="n">
+      <c r="A587" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B587" t="inlineStr">
-        <is>
-          <t>Bart Verbruggen</t>
-        </is>
-      </c>
-      <c r="C587" t="inlineStr">
+      <c r="B587" s="3" t="inlineStr">
+        <is>
+          <t>David Raya Martín</t>
+        </is>
+      </c>
+      <c r="C587" s="3" t="inlineStr">
         <is>
           <t>GK</t>
         </is>
       </c>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E587" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="D587" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E587" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -13287,7 +13287,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Omar Alderete</t>
+          <t>Sepp van den Berg</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13312,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Sepp van den Berg</t>
+          <t>Virgil van Dijk</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -13357,27 +13357,27 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="3" t="n">
+      <c r="A594" t="n">
         <v>32</v>
       </c>
-      <c r="B594" s="3" t="inlineStr">
-        <is>
-          <t>Bruno Borges Fernandes</t>
-        </is>
-      </c>
-      <c r="C594" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D594" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E594" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Cody Gakpo</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13462,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Đorđe Petrović</t>
+          <t>Bart Verbruggen</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -13477,7 +13477,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -13567,7 +13567,7 @@
       <c r="D602" s="5" t="inlineStr"/>
       <c r="E602" s="5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>61</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       <c r="A603" t="inlineStr"/>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Bart Verbruggen in for David Raya Martín</t>
+          <t>Bart Verbruggen in for Emiliano Martínez Romero</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
@@ -13608,7 +13608,7 @@
       <c r="A606" t="inlineStr"/>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Gabriel dos Santos Magalhães in for Trevoh Chalobah</t>
+          <t>Marcus Tavernier in for Cole Palmer</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -13619,7 +13619,7 @@
       <c r="A607" t="inlineStr"/>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Marcus Tavernier in for Cole Palmer</t>
+          <t>Diego Gómez Amarilla in for Enzo Fernández</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -13630,7 +13630,7 @@
       <c r="A608" t="inlineStr"/>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Diego Gómez Amarilla in for Enzo Fernández</t>
+          <t>Erling Haaland in for Norberto Bercique Gomes Betuncal</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -13641,7 +13641,7 @@
       <c r="A609" t="inlineStr"/>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Erling Haaland in for Norberto Bercique Gomes Betuncal</t>
+          <t>Sepp van den Berg in for Pascal Struijk</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -13652,7 +13652,7 @@
       <c r="A610" t="inlineStr"/>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Sepp van den Berg in for Virgil van Dijk</t>
+          <t>Jan Paul van Hecke in for Ibrahima Konaté</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -13663,7 +13663,7 @@
       <c r="A611" t="inlineStr"/>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Jan Paul van Hecke in for Ibrahima Konaté</t>
+          <t>Dominik Szoboszlai in for Bruno Borges Fernandes</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -13674,7 +13674,7 @@
       <c r="A612" t="inlineStr"/>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Dominik Szoboszlai in for Cody Gakpo</t>
+          <t>Marc Guéhi in for Daniel Ballard</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -13685,7 +13685,7 @@
       <c r="A613" t="inlineStr"/>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Omar Alderete in for Malick Thiaw</t>
+          <t>Virgil van Dijk in for Malick Thiaw</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -13720,7 +13720,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Đorđe Petrović</t>
+          <t>Bart Verbruggen</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -13770,7 +13770,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>James Justin</t>
+          <t>Jan Paul van Hecke</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -13785,107 +13785,107 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="620">
-      <c r="A620" t="n">
+      <c r="A620" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B620" t="inlineStr">
-        <is>
-          <t>Jan Paul van Hecke</t>
-        </is>
-      </c>
-      <c r="C620" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D620" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E620" t="inlineStr">
-        <is>
-          <t>12</t>
+      <c r="B620" s="3" t="inlineStr">
+        <is>
+          <t>Marc Guéhi</t>
+        </is>
+      </c>
+      <c r="C620" s="3" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D620" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E620" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="621">
-      <c r="A621" s="3" t="n">
+      <c r="A621" t="n">
         <v>33</v>
       </c>
-      <c r="B621" s="3" t="inlineStr">
-        <is>
-          <t>Marc Guéhi</t>
-        </is>
-      </c>
-      <c r="C621" s="3" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D621" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E621" s="3" t="inlineStr">
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Sepp van den Berg</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>33</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Virgil van Dijk</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
     </row>
-    <row r="622">
-      <c r="A622" s="4" t="n">
+    <row r="623">
+      <c r="A623" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B622" s="4" t="inlineStr">
+      <c r="B623" s="4" t="inlineStr">
         <is>
           <t>Antoine Semenyo</t>
         </is>
       </c>
-      <c r="C622" s="4" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D622" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E622" s="4" t="inlineStr">
+      <c r="C623" s="4" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D623" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E623" s="4" t="inlineStr">
         <is>
           <t>5 (10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="n">
-        <v>33</v>
-      </c>
-      <c r="B623" t="inlineStr">
-        <is>
-          <t>Bruno Borges Fernandes</t>
-        </is>
-      </c>
-      <c r="C623" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D623" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E623" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
     </row>
@@ -13895,7 +13895,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Dominik Szoboszlai</t>
+          <t>Cody Gakpo</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Marcus Tavernier</t>
+          <t>Diego Gómez Amarilla</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -13995,7 +13995,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Bart Verbruggen</t>
+          <t>Robert Lynch Sánchez</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -14020,7 +14020,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Diego Gómez Amarilla</t>
+          <t>Marcus Tavernier</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -14045,12 +14045,12 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Sepp van den Berg</t>
+          <t>Dominik Szoboszlai</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -14100,7 +14100,7 @@
       <c r="D632" s="5" t="inlineStr"/>
       <c r="E632" s="5" t="inlineStr">
         <is>
-          <t>102  [Bench Boost week: bench 15 not in path; chip read]</t>
+          <t>89  [Bench Boost week: bench 18 not in path; chip read]</t>
         </is>
       </c>
     </row>
@@ -14108,7 +14108,7 @@
       <c r="A633" t="inlineStr"/>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Jaka Bijol in for Gabriel dos Santos Magalhães</t>
+          <t>Robert Lynch Sánchez in for David Raya Martín</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -14119,7 +14119,7 @@
       <c r="A634" t="inlineStr"/>
       <c r="B634" t="inlineStr">
         <is>
-          <t>James Justin in for Omar Alderete</t>
+          <t>Jaka Bijol in for Gabriel dos Santos Magalhães</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -14531,7 +14531,7 @@
       <c r="A653" t="inlineStr"/>
       <c r="B653" t="inlineStr">
         <is>
-          <t>David Raya Martín in for Đorđe Petrović</t>
+          <t>Eberechi Eze in for Antoine Semenyo</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -14542,7 +14542,7 @@
       <c r="A654" t="inlineStr"/>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Eberechi Eze in for Antoine Semenyo</t>
+          <t>Mohamed Salah in for Marcus Tavernier</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -14553,7 +14553,7 @@
       <c r="A655" t="inlineStr"/>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Mohamed Salah in for Marcus Tavernier</t>
+          <t>Gabriel dos Santos Magalhães in for Sepp van den Berg</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -14564,7 +14564,7 @@
       <c r="A656" t="inlineStr"/>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Gabriel dos Santos Magalhães in for Sepp van den Berg</t>
+          <t>David Raya Martín in for Bart Verbruggen</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
@@ -14575,7 +14575,7 @@
       <c r="A657" t="inlineStr"/>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Mads Hermansen in for Bart Verbruggen</t>
+          <t>Pedro Porro Sauceda in for Jan Paul van Hecke</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
@@ -14586,7 +14586,7 @@
       <c r="A658" t="inlineStr"/>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Pedro Porro Sauceda in for Jan Paul van Hecke</t>
+          <t>Bruno Borges Fernandes in for Diego Gómez Amarilla</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -14597,7 +14597,7 @@
       <c r="A659" t="inlineStr"/>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Cody Gakpo in for Diego Gómez Amarilla</t>
+          <t>Mads Hermansen in for Robert Lynch Sánchez</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -14641,7 +14641,7 @@
       <c r="A663" t="inlineStr"/>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Brian Brobbey in for Erling Haaland</t>
+          <t>Omar Alderete in for Virgil van Dijk</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -14652,7 +14652,7 @@
       <c r="A664" t="inlineStr"/>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Adam Armstrong in for Dominic Calvert-Lewin</t>
+          <t>Brian Brobbey in for Erling Haaland</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
@@ -14663,7 +14663,7 @@
       <c r="A665" t="inlineStr"/>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Omar Alderete in for James Justin</t>
+          <t>Adam Armstrong in for Dominic Calvert-Lewin</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Đorđe Petrović</t>
+          <t>Robert Lynch Sánchez</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Bruno Borges Fernandes</t>
+          <t>Cody Gakpo</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Marcus Tavernier</t>
+          <t>Dominik Szoboszlai</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -14887,12 +14887,12 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Dominic Calvert-Lewin</t>
+          <t>Marcus Tavernier</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -14912,7 +14912,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Erling Haaland</t>
+          <t>Dominic Calvert-Lewin</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -14927,7 +14927,7 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Igor Thiago Nascimento Rodrigues</t>
+          <t>Erling Haaland</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -14987,12 +14987,12 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Dominik Szoboszlai</t>
+          <t>Jan Paul van Hecke</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
@@ -15002,7 +15002,7 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -15012,12 +15012,12 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Jan Paul van Hecke</t>
+          <t>João Pedro Junqueira de Jesus</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -15067,7 +15067,7 @@
       <c r="D683" s="5" t="inlineStr"/>
       <c r="E683" s="5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       <c r="A684" t="inlineStr"/>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Igor Thiago Nascimento Rodrigues in for João Pedro Junqueira de Jesus</t>
+          <t>Gabriel dos Santos Magalhães in for Jaka Bijol</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -15086,7 +15086,7 @@
       <c r="A685" t="inlineStr"/>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Gabriel dos Santos Magalhães in for Jaka Bijol</t>
+          <t>James Justin in for Virgil van Dijk</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -15249,7 +15249,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Bruno Borges Fernandes</t>
+          <t>Cody Gakpo</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -15319,52 +15319,52 @@
       </c>
     </row>
     <row r="696">
-      <c r="A696" s="4" t="n">
+      <c r="A696" t="n">
         <v>36</v>
       </c>
-      <c r="B696" s="4" t="inlineStr">
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Dominic Calvert-Lewin</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B697" s="4" t="inlineStr">
         <is>
           <t>Erling Haaland</t>
         </is>
       </c>
-      <c r="C696" s="4" t="inlineStr">
+      <c r="C697" s="4" t="inlineStr">
         <is>
           <t>FWD</t>
         </is>
       </c>
-      <c r="D696" s="4" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E696" s="4" t="inlineStr">
+      <c r="D697" s="4" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E697" s="4" t="inlineStr">
         <is>
           <t>11 (22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="n">
-        <v>36</v>
-      </c>
-      <c r="B697" t="inlineStr">
-        <is>
-          <t>Igor Thiago Nascimento Rodrigues</t>
-        </is>
-      </c>
-      <c r="C697" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D697" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E697" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
     </row>
@@ -15374,7 +15374,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Đorđe Petrović</t>
+          <t>Robert Lynch Sánchez</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -15399,7 +15399,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Dominic Calvert-Lewin</t>
+          <t>João Pedro Junqueira de Jesus</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -15479,7 +15479,7 @@
       <c r="D702" s="5" t="inlineStr"/>
       <c r="E702" s="5" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>89</t>
         </is>
       </c>
     </row>
@@ -15645,27 +15645,27 @@
       </c>
     </row>
     <row r="711">
-      <c r="A711" s="3" t="n">
+      <c r="A711" t="n">
         <v>37</v>
       </c>
-      <c r="B711" s="3" t="inlineStr">
-        <is>
-          <t>Bruno Borges Fernandes</t>
-        </is>
-      </c>
-      <c r="C711" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D711" s="3" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E711" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Cody Gakpo</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -15675,47 +15675,47 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
+          <t>Dominik Szoboszlai</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B713" s="3" t="inlineStr">
+        <is>
           <t>Leandro Trossard</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D712" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E712" t="inlineStr">
+      <c r="C713" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D713" s="3" t="inlineStr">
+        <is>
+          <t>Starting 11</t>
+        </is>
+      </c>
+      <c r="E713" s="3" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="n">
-        <v>37</v>
-      </c>
-      <c r="B713" t="inlineStr">
-        <is>
-          <t>Dominic Calvert-Lewin</t>
-        </is>
-      </c>
-      <c r="C713" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D713" t="inlineStr">
-        <is>
-          <t>Starting 11</t>
-        </is>
-      </c>
-      <c r="E713" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
     </row>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Erling Haaland</t>
+          <t>Dominic Calvert-Lewin</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -15750,7 +15750,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Igor Thiago Nascimento Rodrigues</t>
+          <t>Erling Haaland</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -15775,7 +15775,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Đorđe Petrović</t>
+          <t>Robert Lynch Sánchez</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -15790,7 +15790,7 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Diego Gómez Amarilla</t>
+          <t>João Pedro Junqueira de Jesus</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -15865,7 +15865,7 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -15888,7 +15888,7 @@
       <c r="A721" t="inlineStr"/>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Leandro Trossard in for Dominik Szoboszlai</t>
+          <t>Leandro Trossard in for Diego Gómez Amarilla</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -16051,7 +16051,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Bruno Borges Fernandes</t>
+          <t>Cody Gakpo</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -16076,7 +16076,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Diego Gómez Amarilla</t>
+          <t>Dominik Szoboszlai</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Igor Thiago Nascimento Rodrigues</t>
+          <t>João Pedro Junqueira de Jesus</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16176,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Đorđe Petrović</t>
+          <t>Robert Lynch Sánchez</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -16191,7 +16191,7 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -16281,7 +16281,7 @@
       <c r="D738" s="5" t="inlineStr"/>
       <c r="E738" s="5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -16317,7 +16317,7 @@
       <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr"/>
       <c r="E742" t="n">
-        <v>2247</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="743">
@@ -16330,7 +16330,7 @@
       <c r="C743" t="inlineStr"/>
       <c r="D743" t="inlineStr"/>
       <c r="E743" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="744">
@@ -16343,7 +16343,7 @@
       <c r="C744" t="inlineStr"/>
       <c r="D744" t="inlineStr"/>
       <c r="E744" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="745">
@@ -16381,7 +16381,7 @@
       <c r="C747" t="inlineStr"/>
       <c r="D747" t="inlineStr"/>
       <c r="E747" t="n">
-        <v>2283</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="748">
@@ -16394,7 +16394,7 @@
       <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr"/>
       <c r="E748" t="n">
-        <v>2283</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="749">
